--- a/School_Mang/EXCEL/Months/degree-3p.xlsx
+++ b/School_Mang/EXCEL/Months/degree-3p.xlsx
@@ -219,7 +219,29 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="14">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF8B8B"/>
+          <bgColor rgb="FFF3DC53"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC5C5"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -760,7 +782,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="18">
-        <f>ROUND((E5+F5+G5+H5+I5+J5+K5+L5)/8,0)</f>
+        <f>ROUND((J5+I5+H5+G5+E5)/5,0)</f>
         <v>0</v>
       </c>
       <c r="O5" s="7">
@@ -806,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="18">
-        <f t="shared" ref="N6:N69" si="0">ROUND((E6+F6+G6+H6+I6+J6+K6+L6)/8,0)</f>
+        <f t="shared" ref="N6:N69" si="0">ROUND((J6+I6+H6+G6+E6)/5,0)</f>
         <v>0</v>
       </c>
       <c r="O6" s="7">
@@ -3750,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="N70" s="18">
-        <f t="shared" ref="N70:N133" si="1">ROUND((E70+F70+G70+H70+I70+J70+K70+L70)/8,0)</f>
+        <f t="shared" ref="N70:N133" si="1">ROUND((J70+I70+H70+G70+E70)/5,0)</f>
         <v>0</v>
       </c>
       <c r="O70" s="6">
@@ -6694,7 +6716,7 @@
         <v>0</v>
       </c>
       <c r="N134" s="18">
-        <f t="shared" ref="N134:N152" si="2">ROUND((E134+F134+G134+H134+I134+J134+K134+L134)/8,0)</f>
+        <f t="shared" ref="N134:N152" si="2">ROUND((J134+I134+H134+G134+E134)/5,0)</f>
         <v>0</v>
       </c>
       <c r="O134" s="6">
@@ -7522,7 +7544,7 @@
         <v>0</v>
       </c>
       <c r="N152" s="18">
-        <f t="shared" si="2"/>
+        <f>ROUND((J152+I152+H152+G152+E152)/5,0)</f>
         <v>0</v>
       </c>
       <c r="O152" s="6">
@@ -7541,47 +7563,47 @@
     <mergeCell ref="B2:Q2"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:R152">
-    <cfRule type="containsBlanks" dxfId="10" priority="12">
+    <cfRule type="containsBlanks" dxfId="13" priority="12">
       <formula>LEN(TRIM(B5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:N152">
-    <cfRule type="cellIs" dxfId="9" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="9" operator="greaterThan">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5:R152">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="greaterThan">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="5" priority="8">
+    <cfRule type="containsBlanks" dxfId="8" priority="8">
       <formula>LEN(TRIM(R5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O5:O152">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="2" priority="5">
+    <cfRule type="containsBlanks" dxfId="5" priority="5">
       <formula>LEN(TRIM(O5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:A152">
-    <cfRule type="containsBlanks" dxfId="1" priority="2">
+    <cfRule type="containsBlanks" dxfId="4" priority="2">
       <formula>LEN(TRIM(A5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S5:S152">
-    <cfRule type="containsBlanks" dxfId="0" priority="1">
+    <cfRule type="containsBlanks" dxfId="3" priority="1">
       <formula>LEN(TRIM(S5))=0</formula>
     </cfRule>
   </conditionalFormatting>
